--- a/forms/trg/Formulir_TRG_oraclefrg.xlsx
+++ b/forms/trg/Formulir_TRG_oraclefrg.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B30)</f>
+        <f>COUNTA(Anggota!B5:B31)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F30)</f>
+        <f>COUNTA(Anggota!F5:F31)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,15 +925,19 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>drg. M. Irfan Rasul, Ph.D., Sp.B.M.M, Subsp. C.O.M (K)</t>
+          <t>Dr. drg. Andi Tajrin, M.kes., Sp.B.M.M., SubSp. C.O.M.(K)</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
@@ -954,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>drg. Nurwahida, M.KG., Sp.B.M.M., Subsp.C.O.M.(K)</t>
+          <t>drg. M. Irfan Rasul, Ph.D., Sp.B.M.M, Subsp. C.O.M (K)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -983,12 +987,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>drg. Hadira, M.KG., Sp.B.M.M., Subsp.C.O.M.(K)</t>
+          <t>drg. Nurwahida, M.KG., Sp.B.M.M., Subsp.C.O.M.(K)</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1012,19 +1016,15 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>drg. Husni Mubarak Sp.B.M.Mf</t>
+          <t>drg. Hadira, M.KG., Sp.B.M.M., Subsp.C.O.M.(K)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Department of Oral and Maxillofacial Surgery, Faculty of Dentistry, University of Indonesia, Jakarta, Indonesia</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
@@ -1045,15 +1045,19 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Kei Tomihara, D.D.S., Ph.D</t>
+          <t>drg. Husni Mubarak Sp.B.M.Mf</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Department of Oral and Maxillofacial Surgery, Faculty of Dentistry, University of Indonesia, Jakarta, Indonesia</t>
+        </is>
+      </c>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
@@ -1074,12 +1078,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dedy Saputra</t>
+          <t>Prof. Kei Tomihara, D.D.S., Ph.D</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1103,12 +1107,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Indana Zulfa</t>
+          <t>Dedy Saputra</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1132,12 +1136,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Andi Ariaty Bertha</t>
+          <t>Indana Zulfa</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1161,12 +1165,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Bedro Bramanta</t>
+          <t>Andi Ariaty Bertha</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1190,12 +1194,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Alfan Maulana Erdiansyah</t>
+          <t>Bedro Bramanta</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1219,12 +1223,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Nur Amal</t>
+          <t>Alfan Maulana Erdiansyah</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1248,12 +1252,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Reza Irian Rama Putra</t>
+          <t>Nur Amal</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1277,12 +1281,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Andi Rizka Juliana</t>
+          <t>Reza Irian Rama Putra</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1306,12 +1310,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Kasma AS</t>
+          <t>Andi Rizka Juliana</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1333,10 +1337,22 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Kasma AS</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D19" s="12" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>The Thematic Research Group on Orofacial Cleft Research is established to provide a collaborative platform that integrates clinical expertise, biomedical science, public health, and technological innovation to advance understanding, prevention, and management of orofacial clefts. The group aims to strengthen research capacity, foster academic collaboration, and translate scientific findings into improved patient care, education, and policy development</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1344,7 +1360,11 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1533,15 +1553,32 @@
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="12" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
